--- a/ig/nr-add-def-ins-collection/CodeSystem-fr-core-fiabilite-identite.xlsx
+++ b/ig/nr-add-def-ins-collection/CodeSystem-fr-core-fiabilite-identite.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="83">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-16T15:07:43+00:00</t>
+    <t>2023-10-23T11:38:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -120,7 +120,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>19</t>
+    <t>21</t>
   </si>
   <si>
     <t>Level</t>
@@ -240,16 +240,28 @@
     <t>Homonyme détecté</t>
   </si>
   <si>
+    <t>INVA</t>
+  </si>
+  <si>
+    <t>Identité invalidée</t>
+  </si>
+  <si>
     <t>HOMA</t>
   </si>
   <si>
-    <t>Homonyme avéré</t>
-  </si>
-  <si>
-    <t>INVA</t>
-  </si>
-  <si>
-    <t>Identité invalidée</t>
+    <t>Homonyme avéré (attribut d'identité homonyme)</t>
+  </si>
+  <si>
+    <t>FICT</t>
+  </si>
+  <si>
+    <t>Identité fictive (attribut d'identité fictive)</t>
+  </si>
+  <si>
+    <t>DOUT</t>
+  </si>
+  <si>
+    <t>Identité douteuse (attribut d'identité douteuse)</t>
   </si>
 </sst>
 </file>
@@ -565,7 +577,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -810,6 +822,30 @@
       </c>
       <c r="D20" s="2"/>
     </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="C21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="D21" s="2"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="C22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="D22" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/ig/nr-add-def-ins-collection/CodeSystem-fr-core-fiabilite-identite.xlsx
+++ b/ig/nr-add-def-ins-collection/CodeSystem-fr-core-fiabilite-identite.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-23T11:38:46+00:00</t>
+    <t>2023-11-06T10:27:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-def-ins-collection/CodeSystem-fr-core-fiabilite-identite.xlsx
+++ b/ig/nr-add-def-ins-collection/CodeSystem-fr-core-fiabilite-identite.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-06T10:27:25+00:00</t>
+    <t>2023-11-06T10:34:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This code system  includes all the French Identity reliabilty codes (InteropSanté).</t>
+    <t>This code system includes all the French Identity reliabilty codes (InteropSanté).</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -165,7 +165,7 @@
     <t>DESA</t>
   </si>
   <si>
-    <t>Identité ndésactivée</t>
+    <t>Identité désactivée</t>
   </si>
   <si>
     <t>DPOT</t>

--- a/ig/nr-add-def-ins-collection/CodeSystem-fr-core-fiabilite-identite.xlsx
+++ b/ig/nr-add-def-ins-collection/CodeSystem-fr-core-fiabilite-identite.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-06T10:34:42+00:00</t>
+    <t>2023-11-06T13:10:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-def-ins-collection/CodeSystem-fr-core-fiabilite-identite.xlsx
+++ b/ig/nr-add-def-ins-collection/CodeSystem-fr-core-fiabilite-identite.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-06T13:10:33+00:00</t>
+    <t>2023-11-06T13:11:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-def-ins-collection/CodeSystem-fr-core-fiabilite-identite.xlsx
+++ b/ig/nr-add-def-ins-collection/CodeSystem-fr-core-fiabilite-identite.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-06T13:11:32+00:00</t>
+    <t>2023-11-06T13:13:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-def-ins-collection/CodeSystem-fr-core-fiabilite-identite.xlsx
+++ b/ig/nr-add-def-ins-collection/CodeSystem-fr-core-fiabilite-identite.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-06T13:13:14+00:00</t>
+    <t>2023-11-06T13:13:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-def-ins-collection/CodeSystem-fr-core-fiabilite-identite.xlsx
+++ b/ig/nr-add-def-ins-collection/CodeSystem-fr-core-fiabilite-identite.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.fr/ig/fhir/core/CodeSystem/fr-core-fiabilite-identite</t>
+    <t>https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-fiabilite-identite</t>
   </si>
   <si>
     <t>Identifier</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-06T13:13:47+00:00</t>
+    <t>2023-11-08T15:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
